--- a/backend/report.xlsx
+++ b/backend/report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Document Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:F175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DOCUMENT REPORT</t>
+          <t>AUDIT REPORT</t>
         </is>
       </c>
     </row>
@@ -438,7 +438,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Today</t>
         </is>
       </c>
     </row>
@@ -450,7 +450,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13-07-2026</t>
+          <t>14-07-2026</t>
         </is>
       </c>
     </row>
@@ -462,186 +462,423 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06:41 PM</t>
+          <t>12:16 PM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>File Name</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Document Type</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Performed By</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Action Time</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Total Documents</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>170</v>
+          <t>123456.jpeg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:12:32.530502</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Processed</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>65</v>
+          <t>123456.jpeg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Validation Completed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:12:32.528422</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>56</v>
+          <t>123456.jpeg</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Data Extracted</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:12:32.526381</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>9</v>
+          <t>123456.jpeg</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Document Classified</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:12:32.523955</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>105</v>
+          <t>123456.jpeg</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OCR Completed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:12:32.517999</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STP Rate</t>
+          <t>123456.jpeg</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>32.94%</t>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Preprocessing Completed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:12:32.515183</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exception Rate</t>
+          <t>123456.jpeg</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Document Uploaded</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>praveen</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:12:32.507783</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Average Processing Time</t>
+          <t>Shiva_Resume.jpg</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2.5 min</t>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:12:30.881395</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cost Savings</t>
+          <t>Shiva_Resume.jpg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>₹5000</t>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Validation Completed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:12:30.879518</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Shiva_Resume.jpg</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Data Extracted</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:12:30.877336</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>File Name</t>
+          <t>Shiva_Resume.jpg</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Document Type</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Confidence</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Uploaded Time</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Completed Time</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Approved By</t>
+          <t>2026-07-14 12:12:30.873879</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>123456.jpeg</t>
+          <t>Shiva_Resume.jpg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:32.627106</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:32.627106</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:30.868194</t>
         </is>
       </c>
     </row>
@@ -663,71 +900,61 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:30.068124</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:30.068124</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:30.865076</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Praveen_Kumar_Resume.pdf.pdf</t>
+          <t>Shiva_Resume.jpg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:29.156744</t>
+          <t>praveen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:29.156744</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:30.860348</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>invoice12.jpg</t>
+          <t>Praveen_Kumar_Resume.pdf.pdf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -737,29 +964,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5000%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:26.602538</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:26.602538</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:28.039936</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume  (4).doc</t>
+          <t>Praveen_Kumar_Resume.pdf.pdf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -774,34 +996,29 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:26.069567</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:26.069567</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:28.033164</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>invoice123.jpg</t>
+          <t>Praveen_Kumar_Resume.pdf.pdf</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -811,71 +1028,61 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5000%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:24.605280</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:24.605280</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:28.028487</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
+          <t>Praveen_Kumar_Resume.pdf.pdf</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10000%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:23.502810</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:23.502810</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:28.024229</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>invoice1.jpg</t>
+          <t>Praveen_Kumar_Resume.pdf.pdf</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -885,29 +1092,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5000%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:21.760552</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:21.760552</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:28.017247</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pravalya_Resume (1) (1).docx</t>
+          <t>Praveen_Kumar_Resume.pdf.pdf</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -922,29 +1124,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:16.659820</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:16.659820</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:28.012321</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume12.pdf</t>
+          <t>Praveen_Kumar_Resume.pdf.pdf</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -959,29 +1156,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:15.845046</t>
+          <t>praveen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:15.845046</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:28.005221</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>invoice1234.jpg</t>
+          <t>invoice12.jpg</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -996,71 +1188,61 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5000%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:14.112180</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:14.112180</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:27.468240</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>invoice12.jpg</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:13.960239</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-13 12:25:13.960239</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:27.466142</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>123456.jpeg</t>
+          <t>invoice12.jpg</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1070,71 +1252,61 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-13 12:15:00.420082</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-13 12:15:00.420082</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:27.463136</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Shiva_Resume.jpg</t>
+          <t>invoice12.jpg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:56.983671</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:56.983671</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:27.460741</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Praveen_Kumar_Resume.pdf.pdf</t>
+          <t>invoice12.jpg</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1144,22 +1316,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:54.850401</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:54.850401</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:27.457325</t>
         </is>
       </c>
     </row>
@@ -1181,34 +1348,29 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:53.050221</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:53.050221</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:27.451372</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume  (4).doc</t>
+          <t>invoice12.jpg</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1218,34 +1380,29 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:51.389708</t>
+          <t>praveen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:51.389708</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:27.446600</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>invoice123.jpg</t>
+          <t>Praveen_kumar_Resume  (4).doc</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1255,71 +1412,61 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:48.749224</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:48.749224</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:25.080765</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
+          <t>Praveen_kumar_Resume  (4).doc</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9900%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:46.471289</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:46.471289</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:25.076607</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>invoice1.jpg</t>
+          <t>Praveen_kumar_Resume  (4).doc</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1329,29 +1476,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:43.009494</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:43.009494</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:25.071026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pravalya_Resume (1) (1).docx</t>
+          <t>Praveen_kumar_Resume  (4).doc</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1366,29 +1508,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:41.166873</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:41.166873</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:25.065645</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume12.pdf</t>
+          <t>Praveen_kumar_Resume  (4).doc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1403,34 +1540,29 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:40.240387</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:40.240387</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:25.058334</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>invoice1234.jpg</t>
+          <t>Praveen_kumar_Resume  (4).doc</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1440,71 +1572,61 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:38.162329</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:38.162329</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:25.052307</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>Praveen_kumar_Resume  (4).doc</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:38.048893</t>
+          <t>praveen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-13 12:14:38.048893</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:25.046725</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>123456.jpeg</t>
+          <t>invoice123.jpg</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1514,71 +1636,61 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:42.248143</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:42.248143</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:24.512651</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Shiva_Resume.jpg</t>
+          <t>invoice123.jpg</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:39.785011</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:39.785011</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:24.503545</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Praveen_Kumar_Resume.pdf.pdf</t>
+          <t>invoice123.jpg</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1588,29 +1700,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:38.953888</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:38.953888</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:24.496940</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>invoice12.jpg</t>
+          <t>invoice123.jpg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1625,34 +1732,29 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:37.421538</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:37.421538</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:24.491415</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume  (4).doc</t>
+          <t>invoice123.jpg</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1662,22 +1764,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:36.921617</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:36.921617</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:24.483363</t>
         </is>
       </c>
     </row>
@@ -1699,214 +1796,184 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:35.172116</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:35.172116</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:24.477520</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
+          <t>invoice123.jpg</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:34.214456</t>
+          <t>praveen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:34.214456</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:24.467942</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>invoice1.jpg</t>
+          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:32.318431</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:32.318431</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:22.811770</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pravalya_Resume (1) (1).docx</t>
+          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:31.685825</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:31.685825</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:22.808571</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume12.pdf</t>
+          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:30.866433</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:30.866433</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:22.801020</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>invoice1234.jpg</t>
+          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:28.852936</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:28.852936</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:22.794714</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1921,66 +1988,56 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:28.771326</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-13 12:02:28.771326</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:22.789013</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>123456.jpeg</t>
+          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-13 11:57:01.476974</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-13 11:57:01.476974</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:22.784896</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Shiva_Resume.jpg</t>
+          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1990,39 +2047,34 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:58.915028</t>
+          <t>praveen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:58.915028</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:22.777875</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Praveen_Kumar_Resume.pdf.pdf</t>
+          <t>invoice1.jpg</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2032,29 +2084,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:58.187961</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:58.187961</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:21.909388</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>invoice12.jpg</t>
+          <t>invoice1.jpg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2069,34 +2116,29 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:56.271362</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:56.271362</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:21.903210</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume  (4).doc</t>
+          <t>invoice1.jpg</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2106,29 +2148,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:55.782103</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:55.782103</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:21.896917</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>invoice123.jpg</t>
+          <t>invoice1.jpg</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2143,34 +2180,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:54.039776</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:54.039776</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:21.891335</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
+          <t>invoice1.jpg</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2180,22 +2212,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:52.987905</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:52.987905</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:21.884839</t>
         </is>
       </c>
     </row>
@@ -2217,34 +2244,29 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:50.921964</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:50.921964</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:21.878293</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pravalya_Resume (1) (1).docx</t>
+          <t>invoice1.jpg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2254,29 +2276,24 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:50.223974</t>
+          <t>praveen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:50.223974</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:21.868651</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume12.pdf</t>
+          <t>Pravalya_Resume (1) (1).docx</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2291,34 +2308,29 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:49.520628</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:49.520628</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:20.151120</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>invoice1234.jpg</t>
+          <t>Pravalya_Resume (1) (1).docx</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2328,34 +2340,29 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:47.803936</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:47.803936</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:20.147308</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>Pravalya_Resume (1) (1).docx</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2365,29 +2372,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:47.630616</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:47.630616</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:20.142341</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Vaibhav_Shukla_Resume_3+year-1.docx</t>
+          <t>Pravalya_Resume (1) (1).docx</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2397,34 +2399,29 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-07-12 14:26:48.628209</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-12 14:28:48.698446</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>praveen@gmail.com</t>
+          <t>2026-07-14 12:12:20.136978</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>123456.jpeg</t>
+          <t>Pravalya_Resume (1) (1).docx</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2434,71 +2431,61 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:19.081077</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-10 18:21:52.376195</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>praveen@gmail.com</t>
+          <t>2026-07-14 12:12:20.132084</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Shiva_Resume.jpg</t>
+          <t>Pravalya_Resume (1) (1).docx</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:16.099248</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-11 18:33:57.153946</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>praveen@gmail.com</t>
+          <t>2026-07-14 12:12:20.124598</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Praveen_Kumar_Resume.pdf.pdf</t>
+          <t>Pravalya_Resume (1) (1).docx</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2508,71 +2495,61 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:15.151899</t>
+          <t>praveen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-11 18:34:21.849112</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>praveen@gmail.com</t>
+          <t>2026-07-14 12:12:20.116082</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>invoice12.jpg</t>
+          <t>Praveen_kumar_Resume12.pdf</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:12.768507</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:12.768507</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:19.535064</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume  (4).doc</t>
+          <t>Praveen_kumar_Resume12.pdf</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2587,140 +2564,120 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:12.421972</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:12.421972</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:19.530846</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>invoice123.jpg</t>
+          <t>Praveen_kumar_Resume12.pdf</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:10.766281</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:10.766281</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:19.527096</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
+          <t>Praveen_kumar_Resume12.pdf</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10000%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:10.034089</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:10.034089</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:19.523654</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>invoice1.jpg</t>
+          <t>Praveen_kumar_Resume12.pdf</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:08.019980</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:08.019980</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:19.518476</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Pravalya_Resume (1) (1).docx</t>
+          <t>Praveen_kumar_Resume12.pdf</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2735,22 +2692,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:05.777587</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:05.777587</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:19.512988</t>
         </is>
       </c>
     </row>
@@ -2772,22 +2724,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:04.908377</t>
+          <t>praveen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:04.908377</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:19.501754</t>
         </is>
       </c>
     </row>
@@ -2804,76 +2751,66 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:03.268372</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:03.268372</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:18.650655</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>invoice1234.jpg</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:03.163976</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-10 18:08:03.163976</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:18.645767</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>123456.jpeg</t>
+          <t>invoice1234.jpg</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2883,145 +2820,125 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:32.338246</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:32.338246</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:18.640874</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>123456.jpeg</t>
+          <t>invoice1234.jpg</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:31.130378</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-11 18:34:50.713079</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>praveen@gmail.com</t>
+          <t>2026-07-14 12:12:18.634375</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Shiva_Resume.jpg</t>
+          <t>invoice1234.jpg</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:31.118925</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:31.118925</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:18.629264</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Shiva_Resume.jpg</t>
+          <t>invoice1234.jpg</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:27.728480</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:27.728480</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:18.623538</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Praveen_Kumar_Resume.pdf.pdf</t>
+          <t>invoice1234.jpg</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3031,71 +2948,61 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:27.717717</t>
+          <t>praveen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:27.717717</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:18.611602</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Praveen_Kumar_Resume.pdf.pdf</t>
+          <t>Shiva_Resume123456.jpg</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:27.037604</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:27.037604</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:16.716304</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>invoice12.jpg</t>
+          <t>Shiva_Resume123456.jpg</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3105,34 +3012,29 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:27.021852</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:27.021852</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:16.711419</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>invoice12.jpg</t>
+          <t>Shiva_Resume123456.jpg</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3142,108 +3044,93 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:25.620721</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:25.620721</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:16.706444</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume  (4).doc</t>
+          <t>Shiva_Resume123456.jpg</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:25.610828</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:25.610828</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:16.700600</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume  (4).doc</t>
+          <t>Shiva_Resume123456.jpg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:24.810540</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:24.810540</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 12:12:16.695839</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>invoice123.jpg</t>
+          <t>Shiva_Resume123456.jpg</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3253,34 +3140,29 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:24.789803</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:24.789803</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:16.691722</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>invoice123.jpg</t>
+          <t>Shiva_Resume123456.jpg</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3290,177 +3172,152 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:22.117791</t>
+          <t>praveen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:22.117791</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 12:12:16.666837</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
+          <t>123456.jpeg</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:22.098750</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:22.098750</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:14.377414</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
+          <t>123456.jpeg</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:20.663195</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:20.663195</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:14.373049</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>invoice1.jpg</t>
+          <t>123456.jpeg</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:20.652705</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:20.652705</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:14.368017</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>invoice1.jpg</t>
+          <t>123456.jpeg</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:18.760268</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:18.760268</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:14.360831</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Pravalya_Resume (1) (1).docx</t>
+          <t>123456.jpeg</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3475,29 +3332,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:18.743262</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:18.743262</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:14.355983</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Pravalya_Resume (1) (1).docx</t>
+          <t>123456.jpeg</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3512,29 +3364,24 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:17.916034</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:17.916034</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:14.352546</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume12.pdf</t>
+          <t>123456.jpeg</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3549,71 +3396,61 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:17.897688</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:17.897688</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:14.346373</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume12.pdf</t>
+          <t>Shiva_Resume.jpg</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:16.810157</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:16.810157</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:12.115958</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>invoice1234.jpg</t>
+          <t>Shiva_Resume.jpg</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3623,34 +3460,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:16.793876</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:16.793876</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:12.110836</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>invoice1234.jpg</t>
+          <t>Shiva_Resume.jpg</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3660,29 +3492,24 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:15.216008</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:15.216008</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:12.108515</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>Shiva_Resume.jpg</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3697,29 +3524,24 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:15.198961</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:15.198961</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:12.105422</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>Shiva_Resume.jpg</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3734,103 +3556,88 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:15.147584</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-10 09:41:15.147584</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:12.101012</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>123456.jpeg</t>
+          <t>Shiva_Resume.jpg</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:45.237140</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-10 08:50:11.895313</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>praveen@gmail.com</t>
+          <t>2026-07-14 11:26:12.094384</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>123456.jpeg</t>
+          <t>Shiva_Resume.jpg</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:44.323240</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:44.323240</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:12.090083</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Shiva_Resume.jpg</t>
+          <t>Praveen_Kumar_Resume.pdf.pdf</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3845,29 +3652,24 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:44.309986</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:44.309986</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:09.353110</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Shiva_Resume.jpg</t>
+          <t>Praveen_Kumar_Resume.pdf.pdf</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3882,22 +3684,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:42.687418</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:42.687418</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:09.348296</t>
         </is>
       </c>
     </row>
@@ -3919,22 +3716,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:42.680135</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:42.680135</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:09.342650</t>
         </is>
       </c>
     </row>
@@ -3956,29 +3748,24 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:40.607008</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:40.607008</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:09.337632</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>invoice12.jpg</t>
+          <t>Praveen_Kumar_Resume.pdf.pdf</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3988,34 +3775,29 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:40.600702</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-11 18:33:40.932678</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>praveen@gmail.com</t>
+          <t>2026-07-14 11:26:09.333085</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>invoice12.jpg</t>
+          <t>Praveen_Kumar_Resume.pdf.pdf</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4030,29 +3812,24 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:38.790544</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:38.790544</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:09.329586</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume  (4).doc</t>
+          <t>Praveen_Kumar_Resume.pdf.pdf</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4067,34 +3844,29 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:38.783432</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:38.783432</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:09.325797</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume  (4).doc</t>
+          <t>invoice12.jpg</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4104,34 +3876,29 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:37.347488</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:37.347488</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:08.741355</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>invoice123.jpg</t>
+          <t>invoice12.jpg</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4141,34 +3908,29 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:37.342197</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:37.342197</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:08.736749</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>invoice123.jpg</t>
+          <t>invoice12.jpg</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4178,34 +3940,29 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:31.942603</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:31.942603</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:08.731965</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
+          <t>invoice12.jpg</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4215,34 +3972,29 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:31.929518</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:31.929518</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:08.726888</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
+          <t>invoice12.jpg</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4252,34 +4004,29 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:24.496455</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:24.496455</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:08.721711</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>invoice1.jpg</t>
+          <t>invoice12.jpg</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4289,34 +4036,29 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:24.485769</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:24.485769</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:08.715859</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>invoice1.jpg</t>
+          <t>invoice12.jpg</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4326,29 +4068,24 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:22.633066</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:22.633066</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:08.709812</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Pravalya_Resume (1) (1).docx</t>
+          <t>Praveen_kumar_Resume  (4).doc</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4363,29 +4100,24 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:22.614920</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:22.614920</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:06.893421</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Pravalya_Resume (1) (1).docx</t>
+          <t>Praveen_kumar_Resume  (4).doc</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4400,29 +4132,24 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:21.879523</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:21.879523</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:06.887597</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume12.pdf</t>
+          <t>Praveen_kumar_Resume  (4).doc</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4437,29 +4164,24 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:21.861946</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:21.861946</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:06.879343</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume12.pdf</t>
+          <t>Praveen_kumar_Resume  (4).doc</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4474,29 +4196,24 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:21.213119</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:21.213119</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:06.876048</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>invoice1234.jpg</t>
+          <t>Praveen_kumar_Resume  (4).doc</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4511,29 +4228,24 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:21.196664</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:21.196664</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:06.872818</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>invoice1234.jpg</t>
+          <t>Praveen_kumar_Resume  (4).doc</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4548,29 +4260,24 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:19.762216</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:19.762216</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:06.870061</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>Praveen_kumar_Resume  (4).doc</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4585,34 +4292,29 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:19.748506</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:19.748506</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:06.866922</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>invoice123.jpg</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4622,34 +4324,29 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:19.713731</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-10 08:46:19.713731</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:06.388948</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>123456.jpeg</t>
+          <t>invoice123.jpg</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4659,34 +4356,29 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:30.163179</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:30.163179</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:06.378882</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Shiva_Resume.jpg</t>
+          <t>invoice123.jpg</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4696,34 +4388,29 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:28.113376</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:28.113376</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:06.373388</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Praveen_Kumar_Resume.pdf.pdf</t>
+          <t>invoice123.jpg</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4733,71 +4420,61 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:27.296166</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:27.296166</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:06.368055</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>invoice12.jpg</t>
+          <t>invoice123.jpg</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:25.965528</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-07-12 15:28:41.979170</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>praveen@gmail.com</t>
+          <t>2026-07-14 11:26:06.362621</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume  (4).doc</t>
+          <t>invoice123.jpg</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4807,22 +4484,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:25.459028</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:25.459028</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:06.358573</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4506,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4844,22 +4516,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:23.749152</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:23.749152</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:06.354203</t>
         </is>
       </c>
     </row>
@@ -4871,261 +4538,226 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:22.929492</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:22.929492</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:04.747986</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>invoice1.jpg</t>
+          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:21.464135</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:21.464135</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:04.741471</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Pravalya_Resume (1) (1).docx</t>
+          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:20.022980</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:20.022980</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:04.736864</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume12.pdf</t>
+          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:18.980418</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:18.980418</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:04.732043</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>invoice1234.jpg</t>
+          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:17.486238</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:17.486238</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:04.726782</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-07-10 08:41:17.441149</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-07-10 17:57:28.448181</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>praveen@gmail.com</t>
+          <t>2026-07-14 11:26:04.721183</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-07-10 08:38:54.781639</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-07-10 08:38:54.781639</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:04.716210</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>Pravalya_Resume (1) (1).docx</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5140,29 +4772,24 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-07-10 08:37:02.174935</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-07-10 08:37:02.174935</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:04.025650</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>Pravalya_Resume (1) (1).docx</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5177,29 +4804,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-07-10 08:36:14.831559</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-07-10 08:36:14.831559</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:04.018694</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>Pravalya_Resume (1) (1).docx</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5214,29 +4836,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-07-10 08:34:18.691918</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-07-10 08:34:18.691918</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:04.014379</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>123456.jpeg</t>
+          <t>Pravalya_Resume (1) (1).docx</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5251,66 +4868,56 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:40.740979</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:40.740979</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:04.008441</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Shiva_Resume.jpg</t>
+          <t>Pravalya_Resume (1) (1).docx</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:38.262095</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:38.262095</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:04.003344</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Praveen_Kumar_Resume.pdf.pdf</t>
+          <t>Pravalya_Resume (1) (1).docx</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5325,66 +4932,56 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:37.653085</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:37.653085</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:04.000274</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>invoice12.jpg</t>
+          <t>Pravalya_Resume (1) (1).docx</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:36.132564</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:36.132564</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:03.996387</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume  (4).doc</t>
+          <t>Praveen_kumar_Resume12.pdf</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5399,140 +4996,120 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:35.708764</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:35.708764</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:03.200226</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>invoice123.jpg</t>
+          <t>Praveen_kumar_Resume12.pdf</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:34.160887</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:34.160887</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:03.193841</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
+          <t>Praveen_kumar_Resume12.pdf</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>10000%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:33.452457</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:33.452457</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:03.188706</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>invoice1.jpg</t>
+          <t>Praveen_kumar_Resume12.pdf</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:31.813160</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:31.813160</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:03.184092</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Pravalya_Resume (1) (1).docx</t>
+          <t>Praveen_kumar_Resume12.pdf</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5547,22 +5124,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:31.196759</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:31.196759</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:03.178917</t>
         </is>
       </c>
     </row>
@@ -5584,145 +5156,125 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:30.347419</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:30.347419</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:03.174460</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>invoice1234.jpg</t>
+          <t>Praveen_kumar_Resume12.pdf</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:28.692485</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:28.692485</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:03.171304</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Shiva_Resume123456.jpg</t>
+          <t>invoice1234.jpg</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Pending Review</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:28.633586</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-09 11:46:28.633586</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:02.488555</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Shiva_Resume.jpg</t>
+          <t>invoice1234.jpg</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-07-09 11:28:00.457147</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-07-09 11:28:00.457147</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:02.484163</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Praveen_Kumar_Resume.pdf.pdf</t>
+          <t>invoice1234.jpg</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5732,29 +5284,24 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:59.993788</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:59.993788</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:02.479120</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>invoice12.jpg</t>
+          <t>invoice1234.jpg</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5764,39 +5311,34 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:58.962959</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:58.962959</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:02.475101</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume  (4).doc</t>
+          <t>invoice1234.jpg</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5806,29 +5348,24 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:58.599407</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:58.599407</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:02.471734</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>invoice123.jpg</t>
+          <t>invoice1234.jpg</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5838,76 +5375,66 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:57.488527</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:57.488527</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:02.467760</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
+          <t>invoice1234.jpg</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>10000%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:56.566693</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:56.566693</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:02.463322</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>invoice1.jpg</t>
+          <t>Shiva_Resume123456.jpg</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5917,108 +5444,93 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:55.470808</t>
+          <t>System</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:55.470808</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:00.861256</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Pravalya_Resume (1) (1).docx</t>
+          <t>Shiva_Resume123456.jpg</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Validation Completed</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:55.006029</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:55.006029</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:00.855960</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume12.pdf</t>
+          <t>Shiva_Resume123456.jpg</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Data Extracted</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:54.511307</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:54.511307</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:00.848898</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>invoice1234.jpg</t>
+          <t>Shiva_Resume123456.jpg</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6028,22 +5540,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Document Classified</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:53.402492</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:53.402492</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:00.842724</t>
         </is>
       </c>
     </row>
@@ -6065,29 +5572,24 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>OCR Completed</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:53.343651</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-07-09 11:27:53.343651</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:00.837712</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Shiva_Resume.jpg</t>
+          <t>Shiva_Resume123456.jpg</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6102,59 +5604,49 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Preprocessing Completed</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:40.542339</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:40.542339</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 11:26:00.828998</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Praveen_Kumar_Resume.pdf.pdf</t>
+          <t>Shiva_Resume123456.jpg</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Document Uploaded</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:40.078693</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:40.078693</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 11:26:00.809721</t>
         </is>
       </c>
     </row>
@@ -6176,177 +5668,152 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Processing Completed</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:38.476500</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:38.476500</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 09:44:28.318644</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Praveen_kumar_Resume  (4).doc</t>
+          <t>invoice12.jpg</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:38.122033</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:38.122033</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 09:44:28.311302</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>invoice123.jpg</t>
+          <t>123456.jpeg</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Processing Completed</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:36.388580</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:36.388580</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 09:11:47.943066</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
+          <t>123456.jpeg</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:35.463441</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:35.463441</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 09:11:47.902101</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>invoice1.jpg</t>
+          <t>123456.jpeg</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>9000%</t>
+          <t>Processing Completed</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:34.042097</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:34.042097</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>System</t>
+          <t>2026-07-14 09:11:34.741857</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Pravalya_Resume (1) (1).docx</t>
+          <t>123456.jpeg</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6356,545 +5823,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:33.218114</t>
+          <t>praveen@gmail.com</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-07-09 11:04:33.218114</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Praveen_kumar_Resume12.pdf</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>2026-07-09 11:04:32.696276</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-07-09 11:04:32.696276</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>invoice1234.jpg</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>9000%</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>2026-07-09 11:04:30.991187</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-07-09 11:04:30.991187</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Shiva_Resume123456.jpg</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Resume</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>2026-07-09 11:04:30.914149</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-07-09 11:04:30.914149</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Shiva_Resume.jpg</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Resume</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:21.035551</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:19:44.263751</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Praveen_Kumar_Resume.pdf.pdf</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:20.005714</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:18:41.752998</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>praveen@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>invoice12.jpg</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>9000%</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:17.238264</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:17.238264</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Praveen_kumar_Resume  (4).doc</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:16.846333</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:16.846333</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>invoice123.jpg</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>9000%</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:14.993452</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:14.993452</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Praveen  AI_ML_Engineer_Resume.pdf</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Resume</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:14.072172</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:14.072172</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>invoice1.jpg</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>9000%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:11.813877</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:11.813877</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Pravalya_Resume (1) (1).docx</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:10.540563</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:10.540563</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Praveen_kumar_Resume12.pdf</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:09.966834</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-07-11 18:36:03.823675</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>praveen@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>invoice1234.jpg</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>9000%</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:08.205200</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-07-11 18:35:30.042309</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>praveen@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Shiva_Resume123456.jpg</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Resume</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:08.182737</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-07-09 00:16:08.182737</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2026-07-14 09:11:34.707142</t>
         </is>
       </c>
     </row>
